--- a/output/df_primary-logit.xlsx
+++ b/output/df_primary-logit.xlsx
@@ -1733,7 +1733,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.703(0.603–0.804)</t>
+          <t>0.703(0.602 – 0.804)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.703(0.603–0.804)</t>
+          <t>0.703(0.602 – 0.804)</t>
         </is>
       </c>
       <c r="AQ7">
         <v>0.703</v>
       </c>
       <c r="AR7">
-        <v>0.603</v>
+        <v>0.602</v>
       </c>
       <c r="AS7">
         <v>0.804</v>
       </c>
       <c r="AT7">
-        <v>0.05127551020408165</v>
+        <v>0.05153061224489798</v>
       </c>
       <c r="AU7">
         <v>0.861624753007965</v>
       </c>
       <c r="AV7">
-        <v>0.4179809160399949</v>
+        <v>0.4138054400243832</v>
       </c>
       <c r="AW7">
         <v>1.411484609948449</v>
       </c>
       <c r="AX7">
-        <v>0.2534448198746058</v>
+        <v>0.2545099923275679</v>
       </c>
     </row>
     <row r="8">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.878 (0.841–0.915)</t>
+          <t>0.878 (0.839 – 0.917)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.878 (0.841–0.915)</t>
+          <t>0.878 (0.839 – 0.917)</t>
         </is>
       </c>
       <c r="AQ12">
         <v>0.878</v>
       </c>
       <c r="AR12">
-        <v>0.841</v>
+        <v>0.839</v>
       </c>
       <c r="AS12">
-        <v>0.915</v>
+        <v>0.917</v>
       </c>
       <c r="AT12">
-        <v>0.01887755102040818</v>
+        <v>0.01989795918367349</v>
       </c>
       <c r="AU12">
         <v>1.97362554890186</v>
       </c>
       <c r="AV12">
-        <v>1.665687457752716</v>
+        <v>1.650806341482743</v>
       </c>
       <c r="AW12">
-        <v>2.376272808785205</v>
+        <v>2.402266864459867</v>
       </c>
       <c r="AX12">
-        <v>0.1812717732225737</v>
+        <v>0.1916991130043685</v>
       </c>
     </row>
     <row r="13">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>Harrell's C-index</t>
         </is>
       </c>
       <c r="V13">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Under-estimation of risk before recalibration (calibration slope &lt;1; CVD+ CS 0.69, CIL -0.25 - described as near-perfect for CVD+). Near-perfect calibration after simple recalibration (CS 0.96-1.04)</t>
+          <t>Over-estimation of risk before recalibration (calibration slope &lt;1; CVD+ CS 0.69, CIL -0.25 - described as near-perfect for CVD+). Near-perfect calibration after simple recalibration (CS 0.96-1.04)</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Harrell's C-index</t>
+          <t>AUC</t>
         </is>
       </c>
       <c r="V17">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>Harrell's C-index</t>
         </is>
       </c>
       <c r="V18">
